--- a/feedback_forms/013_virtual_assistant_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/013_virtual_assistant_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied',_'value':_0}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied', 'value': 0}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied',_'value':_1}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied', 'value': 1}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied',_'value':_2}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied', 'value': 2}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'support',_'value':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Support', 'value': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'feedback',_'value':_'feedback'}</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Feedback', 'value': 'Feedback'}</t>
+          <t>Feedback</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'suggestion',_'value':_'suggestion'}</t>
+          <t>suggestion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Suggestion', 'value': 'Suggestion'}</t>
+          <t>Suggestion</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'ChatJIMMY', 'value': 'chatjimmy'}</t>
+          <t>ChatJIMMY</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy-2',_'value':_'chatjimmy-2'}</t>
+          <t>chatjimmy-2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy-2', 'value': 'chatjimmy-2'}</t>
+          <t>chatjimmy-2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'user',_'value':_'user'}</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'User', 'value': 'User'}</t>
+          <t>User</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'admin',_'value':_'admin'}</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Admin', 'value': 'Admin'}</t>
+          <t>Admin</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'office',_'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Office', 'value': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'home',_'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Home', 'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'user',_'value':_'user'}</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'User', 'value': 'User'}</t>
+          <t>User</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'admin',_'value':_'admin'}</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Admin', 'value': 'Admin'}</t>
+          <t>Admin</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'local',_'value':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Local', 'value': 'local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'public',_'value':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Public', 'value': 'public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'safari',_'value':_'safari'}</t>
+          <t>safari</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Safari', 'value': 'safari'}</t>
+          <t>Safari</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'chrome',_'value':_'chrome'}</t>
+          <t>chrome</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Chrome', 'value': 'chrome'}</t>
+          <t>Chrome</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'firefox',_'value':_'firefox'}</t>
+          <t>firefox</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Firefox', 'value': 'firefox'}</t>
+          <t>Firefox</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'windows',_'value':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Windows', 'value': 'windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'mac',_'value':_'mac'}</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Mac', 'value': 'mac'}</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'linux',_'value':_'linux'}</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Linux', 'value': 'linux'}</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'windows_10',_'value':_'windows-10'}</t>
+          <t>windows_10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Windows 10', 'value': 'windows-10'}</t>
+          <t>Windows 10</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'windows_7',_'value':_'windows-7'}</t>
+          <t>windows_7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Windows 7', 'value': 'windows-7'}</t>
+          <t>Windows 7</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'mac_os',_'value':_'mac-os'}</t>
+          <t>mac_os</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Mac OS', 'value': 'mac-os'}</t>
+          <t>Mac OS</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'english',_'value':_'en'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'English', 'value': 'en'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'french',_'value':_'fr'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'French', 'value': 'fr'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'spanish',_'value':_'es'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish', 'value': 'es'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'united_states',_'value':_'us'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'United States', 'value': 'us'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'canada',_'value':_'ca'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Canada', 'value': 'ca'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'mexico',_'value':_'mx'}</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Mexico', 'value': 'mx'}</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'north_america',_'value':_'na'}</t>
+          <t>north_america</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'North America', 'value': 'na'}</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'south_america',_'value':_'sa'}</t>
+          <t>south_america</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'South America', 'value': 'sa'}</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'europe',_'value':_'europe'}</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Europe', 'value': 'europe'}</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new-york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'new-york'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'london',_'value':_'london'}</t>
+          <t>london</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'London', 'value': 'london'}</t>
+          <t>London</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'paris',_'value':_'paris'}</t>
+          <t>paris</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Paris', 'value': 'paris'}</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'desktop',_'value':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Desktop', 'value': 'desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'laptop',_'value':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Laptop', 'value': 'laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'mobile',_'value':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile', 'value': 'mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
